--- a/files/港岛-半山区西部-Mount Pokfulam.xlsx
+++ b/files/港岛-半山区西部-Mount Pokfulam.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -872,7 +872,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -938,7 +938,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1330,7 +1330,7 @@
         <is>
           <t>薄扶林道86A号
 3643呎 (4+房)
-(25年-09月-17日)
+(25年-09月-18日)
 $1.59亿
 $43,752/呎</t>
         </is>
@@ -1348,7 +1348,7 @@
         <is>
           <t>薄扶林道86C号
 4683呎 (3房)
-(25年-04月-29日)
+(25年-04月-30日)
 $2.30亿
 $49,220/呎</t>
         </is>
@@ -1357,7 +1357,7 @@
         <is>
           <t>薄扶林道86D号
 4765呎 (4+房)
-(24年-05月-09日)
+(24年-05月-10日)
 $3.34亿
 $70,000/呎</t>
         </is>
@@ -1366,7 +1366,7 @@
         <is>
           <t>薄扶林道86E号
 4578呎 (4+房)
-(25年-08月-26日)
+(25年-08月-27日)
 $1.89亿
 $41,337/呎</t>
         </is>
